--- a/exports/trend_1d/MFSL_full_report.xlsx
+++ b/exports/trend_1d/MFSL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.95</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42059</v>
+        <v>42060</v>
       </c>
       <c r="H2" t="n">
-        <v>213.3</v>
+        <v>209.5</v>
       </c>
       <c r="I2" t="n">
         <v>211.12303734945</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>11.91</v>
+        <v>9.92</v>
       </c>
       <c r="L2" t="n">
         <v>0.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.63</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42142</v>
+        <v>42143</v>
       </c>
       <c r="H3" t="n">
-        <v>215.3</v>
+        <v>223</v>
       </c>
       <c r="I3" t="n">
         <v>222.3742232365074</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.77</v>
+        <v>-6.44</v>
       </c>
       <c r="L3" t="n">
         <v>18.19</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.15</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42241</v>
+        <v>42242</v>
       </c>
       <c r="H4" t="n">
-        <v>245</v>
+        <v>237.4</v>
       </c>
       <c r="I4" t="n">
         <v>243.5889456417235</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K4" t="n">
-        <v>9.869999999999999</v>
+        <v>6.46</v>
       </c>
       <c r="L4" t="n">
         <v>4.71</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>17.12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42324</v>
+        <v>42325</v>
       </c>
       <c r="H5" t="n">
-        <v>256.7</v>
+        <v>261.8</v>
       </c>
       <c r="I5" t="n">
         <v>261.5709340887396</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.130000000000001</v>
+        <v>-10.28</v>
       </c>
       <c r="L5" t="n">
         <v>14.57</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>9.43</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42346</v>
+        <v>42347</v>
       </c>
       <c r="H6" t="n">
-        <v>251.7</v>
+        <v>245.4</v>
       </c>
       <c r="I6" t="n">
         <v>248.9862883592901</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.86</v>
+        <v>-6.26</v>
       </c>
       <c r="L6" t="n">
-        <v>4.93</v>
+        <v>6.88</v>
       </c>
       <c r="M6" t="n">
         <v>1.16</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42394</v>
+        <v>42396</v>
       </c>
       <c r="H7" t="n">
-        <v>224.7</v>
+        <v>348.6</v>
       </c>
       <c r="I7" t="n">
         <v>243.6656436159841</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
-        <v>8.44</v>
+        <v>-42.05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.89</v>
+        <v>42.05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>47.75</v>
       </c>
       <c r="N7" t="n">
-        <v>4.15</v>
+        <v>55.14</v>
       </c>
       <c r="O7" t="n">
         <v>-2.5</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>20.7</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42600</v>
+        <v>42601</v>
       </c>
       <c r="H8" t="n">
-        <v>507</v>
+        <v>498.95</v>
       </c>
       <c r="I8" t="n">
         <v>499.848492709947</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K8" t="n">
-        <v>45.44</v>
+        <v>43.13</v>
       </c>
       <c r="L8" t="n">
         <v>13.14</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>17.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42612</v>
+        <v>42613</v>
       </c>
       <c r="H9" t="n">
-        <v>565.35</v>
+        <v>579.8</v>
       </c>
       <c r="I9" t="n">
         <v>578.2454319100664</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.31</v>
+        <v>-16.2</v>
       </c>
       <c r="L9" t="n">
-        <v>14.13</v>
+        <v>16.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
       <c r="N9" t="n">
         <v>3.43</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>13.44</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H10" t="n">
-        <v>558</v>
+        <v>492.9</v>
       </c>
       <c r="I10" t="n">
         <v>533.7150170196323</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.76</v>
+        <v>-14.99</v>
       </c>
       <c r="L10" t="n">
-        <v>10.31</v>
+        <v>16.19</v>
       </c>
       <c r="M10" t="n">
         <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.79</v>
+        <v>11.67</v>
       </c>
       <c r="O10" t="n">
         <v>2.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>20.9</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42766</v>
+        <v>42767</v>
       </c>
       <c r="H11" t="n">
-        <v>564.65</v>
+        <v>581.7</v>
       </c>
       <c r="I11" t="n">
         <v>576.8308734047716</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K11" t="n">
-        <v>-14.56</v>
+        <v>-18.02</v>
       </c>
       <c r="L11" t="n">
-        <v>17.47</v>
+        <v>22.22</v>
       </c>
       <c r="M11" t="n">
         <v>1.95</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.77</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42786</v>
+        <v>42787</v>
       </c>
       <c r="H12" t="n">
-        <v>594.75</v>
+        <v>564.85</v>
       </c>
       <c r="I12" t="n">
         <v>565.4185448297789</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>2.24</v>
+        <v>-2.9</v>
       </c>
       <c r="L12" t="n">
         <v>3.87</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>5.03</v>
       </c>
       <c r="O12" t="n">
         <v>3.02</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>12.35</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42828</v>
+        <v>42830</v>
       </c>
       <c r="H13" t="n">
-        <v>567.7</v>
+        <v>595.55</v>
       </c>
       <c r="I13" t="n">
         <v>581.6343212546061</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5</v>
+        <v>-5.44</v>
       </c>
       <c r="L13" t="n">
-        <v>3.91</v>
+        <v>7.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.76</v>
       </c>
       <c r="N13" t="n">
-        <v>3.61</v>
+        <v>4.91</v>
       </c>
       <c r="O13" t="n">
         <v>-5.03</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.21</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H14" t="n">
-        <v>621.5</v>
+        <v>569.8</v>
       </c>
       <c r="I14" t="n">
         <v>612.0969106121852</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>4.36</v>
+        <v>-4.32</v>
       </c>
       <c r="L14" t="n">
-        <v>5.97</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>3.22</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>8.32</v>
       </c>
       <c r="O14" t="n">
         <v>4.91</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>16.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42996</v>
+        <v>42997</v>
       </c>
       <c r="H15" t="n">
-        <v>628.55</v>
+        <v>646.55</v>
       </c>
       <c r="I15" t="n">
         <v>631.5797581014032</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.31</v>
+        <v>-13.47</v>
       </c>
       <c r="L15" t="n">
-        <v>12.36</v>
+        <v>14.58</v>
       </c>
       <c r="M15" t="n">
         <v>1.22</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.41</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H16" t="n">
-        <v>606.15</v>
+        <v>587.8</v>
       </c>
       <c r="I16" t="n">
         <v>593.2362438410856</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.25</v>
+        <v>-9.09</v>
       </c>
       <c r="L16" t="n">
-        <v>6.74</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0.61</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
         <v>2.86</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.72</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H17" t="n">
-        <v>575.1</v>
+        <v>590.65</v>
       </c>
       <c r="I17" t="n">
         <v>582.7246452454896</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>2.16</v>
+        <v>-0.48</v>
       </c>
       <c r="L17" t="n">
         <v>3.83</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.76</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H18" t="n">
-        <v>555.7</v>
+        <v>549.65</v>
       </c>
       <c r="I18" t="n">
         <v>552.9110933209836</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.92</v>
+        <v>-6.94</v>
       </c>
       <c r="L18" t="n">
-        <v>7.22</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>0.78</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43209</v>
+        <v>43210</v>
       </c>
       <c r="H19" t="n">
-        <v>448.65</v>
+        <v>478.65</v>
       </c>
       <c r="I19" t="n">
         <v>476.0750335566272</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K19" t="n">
-        <v>18.38</v>
+        <v>12.92</v>
       </c>
       <c r="L19" t="n">
         <v>1.87</v>
@@ -1524,7 +1751,7 @@
         <v>1.59</v>
       </c>
       <c r="N19" t="n">
-        <v>3.19</v>
+        <v>6.69</v>
       </c>
       <c r="O19" t="n">
         <v>-1.09</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>13.11</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H20" t="n">
-        <v>488.15</v>
+        <v>460.6</v>
       </c>
       <c r="I20" t="n">
         <v>463.2962519012023</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K20" t="n">
-        <v>1.98</v>
+        <v>-3.77</v>
       </c>
       <c r="L20" t="n">
         <v>6.22</v>
@@ -1581,7 +1820,7 @@
         <v>1.17</v>
       </c>
       <c r="N20" t="n">
-        <v>3.78</v>
+        <v>5.64</v>
       </c>
       <c r="O20" t="n">
         <v>6.69</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>15.34</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H21" t="n">
-        <v>453.7</v>
+        <v>467.85</v>
       </c>
       <c r="I21" t="n">
         <v>466.0639392882057</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5</v>
+        <v>-1.57</v>
       </c>
       <c r="L21" t="n">
         <v>9.640000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>14.23</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43326</v>
+        <v>43328</v>
       </c>
       <c r="H22" t="n">
-        <v>467.5</v>
+        <v>464.75</v>
       </c>
       <c r="I22" t="n">
         <v>466.3654958927393</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="L22" t="n">
         <v>4.24</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>13.61</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H23" t="n">
-        <v>473.45</v>
+        <v>504.65</v>
       </c>
       <c r="I23" t="n">
         <v>494.2559358149458</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.87</v>
+        <v>-8.59</v>
       </c>
       <c r="L23" t="n">
-        <v>7.04</v>
+        <v>11.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0.97</v>
+        <v>2.12</v>
       </c>
       <c r="N23" t="n">
-        <v>5.15</v>
+        <v>6.59</v>
       </c>
       <c r="O23" t="n">
         <v>-0.59</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.78</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43369</v>
+        <v>43370</v>
       </c>
       <c r="H24" t="n">
-        <v>443.15</v>
+        <v>419.05</v>
       </c>
       <c r="I24" t="n">
         <v>430.0830477909046</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="n">
-        <v>-12.19</v>
+        <v>-16.96</v>
       </c>
       <c r="L24" t="n">
         <v>17.57</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>22.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43420</v>
+        <v>43423</v>
       </c>
       <c r="H25" t="n">
-        <v>420.5</v>
+        <v>437.55</v>
       </c>
       <c r="I25" t="n">
         <v>434.360381036334</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.35</v>
+        <v>-4.41</v>
       </c>
       <c r="L25" t="n">
         <v>6.88</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>17.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H26" t="n">
-        <v>429.4</v>
+        <v>400.15</v>
       </c>
       <c r="I26" t="n">
         <v>412.0100018497408</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.86</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>8.800000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="M26" t="n">
         <v>2.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.85</v>
+        <v>6.81</v>
       </c>
       <c r="O26" t="n">
         <v>4.05</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>15.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H27" t="n">
-        <v>428.85</v>
+        <v>429.7</v>
       </c>
       <c r="I27" t="n">
         <v>429.4304771138361</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.17</v>
+        <v>-7.38</v>
       </c>
       <c r="L27" t="n">
-        <v>7.65</v>
+        <v>9.58</v>
       </c>
       <c r="M27" t="n">
         <v>1.96</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H28" t="n">
-        <v>424.45</v>
+        <v>407.95</v>
       </c>
       <c r="I28" t="n">
         <v>411.935442008417</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.22</v>
+        <v>-5.06</v>
       </c>
       <c r="L28" t="n">
-        <v>4.38</v>
+        <v>5.68</v>
       </c>
       <c r="M28" t="n">
         <v>0.73</v>
       </c>
       <c r="N28" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="O28" t="n">
         <v>0.2</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>13.93</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>428.2</v>
+        <v>445.75</v>
       </c>
       <c r="I29" t="n">
         <v>441.1662342543418</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.96</v>
+        <v>-9.27</v>
       </c>
       <c r="L29" t="n">
-        <v>7.12</v>
+        <v>10.06</v>
       </c>
       <c r="M29" t="n">
         <v>2.99</v>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
         <v>-3.89</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>12.73</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43683</v>
+        <v>43684</v>
       </c>
       <c r="H30" t="n">
-        <v>413.3</v>
+        <v>394.6</v>
       </c>
       <c r="I30" t="n">
         <v>399.8357984024277</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.28</v>
+        <v>-11.48</v>
       </c>
       <c r="L30" t="n">
-        <v>10.56</v>
+        <v>13.94</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.78</v>
+        <v>4.52</v>
       </c>
       <c r="O30" t="n">
         <v>4.1</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>16.41</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43775</v>
+        <v>43776</v>
       </c>
       <c r="H31" t="n">
-        <v>438.7</v>
+        <v>478.25</v>
       </c>
       <c r="I31" t="n">
         <v>441.72215255938</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.18</v>
+        <v>-21.2</v>
       </c>
       <c r="L31" t="n">
-        <v>17.32</v>
+        <v>23.94</v>
       </c>
       <c r="M31" t="n">
         <v>1.64</v>
       </c>
       <c r="N31" t="n">
-        <v>7.02</v>
+        <v>9.02</v>
       </c>
       <c r="O31" t="n">
         <v>-4.52</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.83</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H32" t="n">
-        <v>558.85</v>
+        <v>505.3</v>
       </c>
       <c r="I32" t="n">
         <v>514.2592370305978</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>16.85</v>
+        <v>5.66</v>
       </c>
       <c r="L32" t="n">
         <v>13.41</v>
@@ -2265,7 +2648,7 @@
         <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.58</v>
+        <v>9.58</v>
       </c>
       <c r="O32" t="n">
         <v>9.02</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>16.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43880</v>
+        <v>43881</v>
       </c>
       <c r="H33" t="n">
-        <v>516.75</v>
+        <v>565</v>
       </c>
       <c r="I33" t="n">
         <v>538.6687937242936</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.27</v>
+        <v>-11.81</v>
       </c>
       <c r="L33" t="n">
-        <v>12.45</v>
+        <v>18.16</v>
       </c>
       <c r="M33" t="n">
-        <v>2.12</v>
+        <v>4.89</v>
       </c>
       <c r="N33" t="n">
-        <v>9.15</v>
+        <v>9.34</v>
       </c>
       <c r="O33" t="n">
         <v>-9.58</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.97</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43895</v>
+        <v>43896</v>
       </c>
       <c r="H34" t="n">
-        <v>605.2</v>
+        <v>520.8</v>
       </c>
       <c r="I34" t="n">
         <v>523.2191489131169</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>7.12</v>
+        <v>-7.82</v>
       </c>
       <c r="L34" t="n">
-        <v>4.07</v>
+        <v>15.58</v>
       </c>
       <c r="M34" t="n">
-        <v>1.79</v>
+        <v>7.51</v>
       </c>
       <c r="N34" t="n">
-        <v>3.41</v>
+        <v>13.95</v>
       </c>
       <c r="O34" t="n">
         <v>9.34</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>20.28</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43948</v>
+        <v>43949</v>
       </c>
       <c r="H35" t="n">
-        <v>451.95</v>
+        <v>477.15</v>
       </c>
       <c r="I35" t="n">
         <v>464.7826506396626</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K35" t="n">
-        <v>13.22</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>7.48</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>30.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44432</v>
+        <v>44433</v>
       </c>
       <c r="H36" t="n">
-        <v>1043.8</v>
+        <v>1021.35</v>
       </c>
       <c r="I36" t="n">
         <v>1024.673569268453</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K36" t="n">
-        <v>118.76</v>
+        <v>114.05</v>
       </c>
       <c r="L36" t="n">
         <v>14.67</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>332</v>
+        <v>333</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>17</v>
+      </c>
+      <c r="U36" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.32</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H37" t="n">
-        <v>980.35</v>
+        <v>1017.35</v>
       </c>
       <c r="I37" t="n">
         <v>1005.55379827311</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K37" t="n">
-        <v>4.01</v>
+        <v>0.39</v>
       </c>
       <c r="L37" t="n">
         <v>11.32</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>10.61</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H38" t="n">
-        <v>972.1</v>
+        <v>933.25</v>
       </c>
       <c r="I38" t="n">
         <v>967.0718075520874</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.45</v>
+        <v>-8.27</v>
       </c>
       <c r="L38" t="n">
-        <v>5.05</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>0.89</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
         <v>3.77</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.81</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H39" t="n">
-        <v>772.7</v>
+        <v>794.7</v>
       </c>
       <c r="I39" t="n">
         <v>783.4409434019733</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>14.85</v>
       </c>
       <c r="L39" t="n">
         <v>4.14</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.38</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44781</v>
+        <v>44783</v>
       </c>
       <c r="H40" t="n">
-        <v>794.9</v>
+        <v>779.5</v>
       </c>
       <c r="I40" t="n">
         <v>787.3168157849136</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03</v>
+        <v>-1.91</v>
       </c>
       <c r="L40" t="n">
         <v>3.74</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.79</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H41" t="n">
-        <v>694.65</v>
+        <v>705.6</v>
       </c>
       <c r="I41" t="n">
         <v>700.3539647188109</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K41" t="n">
-        <v>10.89</v>
+        <v>9.48</v>
       </c>
       <c r="L41" t="n">
         <v>9.93</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.84</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H42" t="n">
-        <v>835.65</v>
+        <v>752.95</v>
       </c>
       <c r="I42" t="n">
         <v>795.3881046947569</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K42" t="n">
-        <v>18.43</v>
+        <v>6.71</v>
       </c>
       <c r="L42" t="n">
         <v>6.97</v>
@@ -2835,7 +3338,7 @@
         <v>1.74</v>
       </c>
       <c r="N42" t="n">
-        <v>2.61</v>
+        <v>9.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.58</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>17.88</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H43" t="n">
-        <v>663.6</v>
+        <v>674.9</v>
       </c>
       <c r="I43" t="n">
         <v>670.1627881093876</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K43" t="n">
-        <v>11.87</v>
+        <v>10.37</v>
       </c>
       <c r="L43" t="n">
         <v>14.46</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45274</v>
+        <v>45275</v>
       </c>
       <c r="H44" t="n">
-        <v>1018.3</v>
+        <v>973.9</v>
       </c>
       <c r="I44" t="n">
         <v>985.8428076891057</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K44" t="n">
-        <v>50.88</v>
+        <v>44.3</v>
       </c>
       <c r="L44" t="n">
         <v>5.8</v>
@@ -2949,7 +3476,7 @@
         <v>1.33</v>
       </c>
       <c r="N44" t="n">
-        <v>4.12</v>
+        <v>4.36</v>
       </c>
       <c r="O44" t="n">
         <v>1.7</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.47</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="H45" t="n">
-        <v>913</v>
+        <v>960.25</v>
       </c>
       <c r="I45" t="n">
         <v>958.0138853445784</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K45" t="n">
-        <v>6.25</v>
+        <v>1.4</v>
       </c>
       <c r="L45" t="n">
         <v>5.68</v>
       </c>
       <c r="M45" t="n">
-        <v>1.07</v>
+        <v>2.08</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="O45" t="n">
         <v>-4.36</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.41</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H46" t="n">
-        <v>982.8</v>
+        <v>962.7</v>
       </c>
       <c r="I46" t="n">
         <v>964.4270662969946</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K46" t="n">
-        <v>2.35</v>
+        <v>0.26</v>
       </c>
       <c r="L46" t="n">
         <v>4.92</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.31</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="H47" t="n">
-        <v>992.85</v>
+        <v>1013.4</v>
       </c>
       <c r="I47" t="n">
         <v>1006.537027035976</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.13</v>
+        <v>-5.27</v>
       </c>
       <c r="L47" t="n">
         <v>6.99</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45520</v>
+        <v>45523</v>
       </c>
       <c r="H48" t="n">
-        <v>1017.25</v>
+        <v>991.5</v>
       </c>
       <c r="I48" t="n">
         <v>1015.574705498448</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>0.38</v>
+        <v>-2.16</v>
       </c>
       <c r="L48" t="n">
         <v>2.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>14.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45538</v>
+        <v>45539</v>
       </c>
       <c r="H49" t="n">
-        <v>1128.3</v>
+        <v>1133.3</v>
       </c>
       <c r="I49" t="n">
         <v>1131.114905585628</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.8</v>
+        <v>-14.3</v>
       </c>
       <c r="L49" t="n">
-        <v>14.36</v>
+        <v>16.28</v>
       </c>
       <c r="M49" t="n">
         <v>1.44</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.17</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="H50" t="n">
-        <v>1173.5</v>
+        <v>1166.45</v>
       </c>
       <c r="I50" t="n">
         <v>1171.558126174575</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K50" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="L50" t="n">
         <v>2.5</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H51" t="n">
-        <v>1075.8</v>
+        <v>1102.2</v>
       </c>
       <c r="I51" t="n">
         <v>1093.282509319231</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K51" t="n">
-        <v>7.77</v>
+        <v>5.51</v>
       </c>
       <c r="L51" t="n">
         <v>3.3</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.59</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="H52" t="n">
-        <v>1569.3</v>
+        <v>1537.6</v>
       </c>
       <c r="I52" t="n">
         <v>1549.04453805896</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K52" t="n">
-        <v>42.38</v>
+        <v>39.5</v>
       </c>
       <c r="L52" t="n">
         <v>2.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.91</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H53" t="n">
-        <v>1556.4</v>
+        <v>1588.4</v>
       </c>
       <c r="I53" t="n">
         <v>1565.336439203894</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.22</v>
+        <v>-3.3</v>
       </c>
       <c r="L53" t="n">
-        <v>2.95</v>
+        <v>3.77</v>
       </c>
       <c r="M53" t="n">
         <v>2.62</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.58</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H54" t="n">
-        <v>1564.1</v>
+        <v>1538</v>
       </c>
       <c r="I54" t="n">
         <v>1550.416800113229</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.53</v>
+        <v>-3.17</v>
       </c>
       <c r="L54" t="n">
         <v>3.36</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H55" t="n">
-        <v>1584.2</v>
+        <v>1618.1</v>
       </c>
       <c r="I55" t="n">
         <v>1612.360389798319</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K55" t="n">
-        <v>-3</v>
+        <v>-5.21</v>
       </c>
       <c r="L55" t="n">
         <v>7.15</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.18</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H56" t="n">
-        <v>1627.7</v>
+        <v>1599</v>
       </c>
       <c r="I56" t="n">
         <v>1612.380362833991</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K56" t="n">
-        <v>0.59</v>
+        <v>-1.18</v>
       </c>
       <c r="L56" t="n">
         <v>3.46</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.97</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H57" t="n">
-        <v>1674.7</v>
+        <v>1708.2</v>
       </c>
       <c r="I57" t="n">
         <v>1698.404489111925</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.73</v>
+        <v>-6.83</v>
       </c>
       <c r="L57" t="n">
-        <v>5.35</v>
+        <v>7.03</v>
       </c>
       <c r="M57" t="n">
         <v>1.33</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H58" t="n">
-        <v>1806.8</v>
+        <v>1747.8</v>
       </c>
       <c r="I58" t="n">
         <v>1748.125298538804</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>5.77</v>
+        <v>2.32</v>
       </c>
       <c r="L58" t="n">
         <v>2.97</v>
@@ -3747,7 +4442,7 @@
         <v>2.64</v>
       </c>
       <c r="N58" t="n">
-        <v>2.34</v>
+        <v>3.27</v>
       </c>
       <c r="O58" t="n">
         <v>2</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H59" t="n">
-        <v>1607.4</v>
+        <v>1654.8</v>
       </c>
       <c r="I59" t="n">
         <v>1621.245353153749</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>8.029999999999999</v>
+        <v>5.32</v>
       </c>
       <c r="L59" t="n">
         <v>2.12</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>12.05</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="H60" t="n">
-        <v>1595.4</v>
+        <v>1559.6</v>
       </c>
       <c r="I60" t="n">
         <v>1586.372378501015</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.59</v>
+        <v>-5.75</v>
       </c>
       <c r="L60" t="n">
-        <v>5.73</v>
+        <v>6.88</v>
       </c>
       <c r="M60" t="n">
         <v>1.81</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.68</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H61" t="n">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="I61" t="n">
         <v>1568.928639755675</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K61" t="n">
-        <v>0.04</v>
+        <v>-0.6</v>
       </c>
       <c r="L61" t="n">
         <v>9.869999999999999</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.75</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H62" t="n">
-        <v>1562.9</v>
+        <v>1410</v>
       </c>
       <c r="I62" t="n">
         <v>1432.211010010672</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.39</v>
+        <v>-10.13</v>
       </c>
       <c r="L62" t="n">
-        <v>1.49</v>
+        <v>13.31</v>
       </c>
       <c r="M62" t="n">
-        <v>0.49</v>
+        <v>9.99</v>
       </c>
       <c r="N62" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O62" t="n">
         <v>0.64</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>23</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.59999999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -9053,7 +9816,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -9063,7 +9826,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -9073,7 +9836,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.9</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="14">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.87</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.369999999999999</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.22</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>118.76</v>
+        <v>114.05</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.46</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.22</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="21">
@@ -9153,7 +9916,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.19</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="22">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="25">
@@ -9193,7 +9956,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="26">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.59</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="27">
@@ -9213,7 +9976,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.24</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="28">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
